--- a/매매기록.xlsx
+++ b/매매기록.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1503,6 +1503,78 @@
         <v>2115.91</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>005930.KS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>181200</v>
+      </c>
+      <c r="H34" t="n">
+        <v>181200</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>000660.KS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>880000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>880000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
